--- a/reports/pdf_rolling5_20260821.xlsx
+++ b/reports/pdf_rolling5_20260821.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-13 ~ 2026-08-21  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-13 ~ 2026-08-21  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 412억(8.4%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 17종목  /  매도 19종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 123억(2.6%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 20종목  /  매도 25종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -658,23 +658,23 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>감성코퍼레이션</t>
+          <t>코미코  (신규)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>113</v>
+        <v>420</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>455390000</v>
+        <v>9522240000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.45%→0.50%</t>
+          <t>0.00%→2.04%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>440→553</t>
+          <t>0→420</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-189</v>
+        <v>-283</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1890907200</v>
+        <v>-2866676800</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.59%</t>
+          <t>1.02%→0.37%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>452→263</t>
+          <t>452→169</t>
         </is>
       </c>
     </row>
@@ -706,283 +706,283 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4752800000</v>
+        <v>7438080000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→1.59%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>0→100</t>
+          <t>0→149</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-79</v>
+        <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-3007056000</v>
+        <v>-1340310400</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>1.58%→1.01%</t>
+          <t>0.79%→0.43%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>198→119</t>
+          <t>253→152</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>큐리언트</t>
+          <t>감성코퍼레이션</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1418040000</v>
+        <v>461853600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>1.10%→1.52%</t>
+          <t>0.45%→0.48%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>204→258</t>
+          <t>440→553</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-66</v>
+        <v>-93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-885456000</v>
+        <v>-1343440800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.56%</t>
+          <t>0.89%→0.53%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>253→187</t>
+          <t>263→170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>큐리언트</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2650336000</v>
+        <v>1950624000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>1.40%→1.86%</t>
+          <t>1.10%→1.60%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>98→144</t>
+          <t>204→276</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-62</v>
+        <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-925288000</v>
+        <v>-3031704000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.67%</t>
+          <t>1.58%→0.98%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>263→201</t>
+          <t>198→119</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>477162400</v>
+        <v>2669472000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.63%→0.71%</t>
+          <t>1.40%→1.79%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>244→287</t>
+          <t>98→144</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>씨어스  (편출)</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-36</v>
+        <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-950976000</v>
+        <v>-1414816000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.00%</t>
+          <t>0.61%→0.29%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>36→0</t>
+          <t>74→36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>447283200</v>
+        <v>478951200</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.90%→1.88%</t>
+          <t>0.63%→0.68%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>749→791</t>
+          <t>244→287</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨어스  (편출)</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-27</v>
+        <v>-36</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2237976000</v>
+        <v>-950976000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.58%→1.95%</t>
+          <t>0.21%→0.00%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>132→105</t>
+          <t>36→0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>912600000</v>
+        <v>451651200</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.42%</t>
+          <t>1.90%→1.82%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>233→272</t>
+          <t>749→791</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-25</v>
+        <v>-27</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-889200000</v>
+        <v>-2316600000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.39%</t>
+          <t>2.58%→1.93%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>74→49</t>
+          <t>132→105</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>441417600</v>
+        <v>920712000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1.07%→1.06%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>349→385</t>
+          <t>233→272</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -994,11 +994,11 @@
         <v>-25</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2917200000</v>
+        <v>-3000400000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>4.09%→3.73%</t>
+          <t>4.09%→3.68%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>947232000</v>
+        <v>449280000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.73%→1.04%</t>
+          <t>1.07%→1.03%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>94→118</t>
+          <t>349→385</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1038,11 +1038,11 @@
         <v>-24</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-954720000</v>
+        <v>-968448000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.82%→0.66%</t>
+          <t>0.82%→0.64%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -1054,155 +1054,155 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>970632000</v>
+        <v>1013376000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.70%</t>
+          <t>0.73%→1.07%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>116→133</t>
+          <t>94→118</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-15</v>
+        <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-906360000</v>
+        <v>-464048000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.54%</t>
+          <t>3.53%→3.30%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>55→40</t>
+          <t>787→764</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>410176000</v>
+        <v>885768000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.49%→0.55%</t>
+          <t>1.26%→1.48%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>80→96</t>
+          <t>116→133</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1269632000</v>
+        <v>-901680000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.86%→0.53%</t>
+          <t>0.75%→0.52%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>40→26</t>
+          <t>55→40</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1583400000</v>
+        <v>411840000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.88%→1.18%</t>
+          <t>0.49%→0.53%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>80→96</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-212399200</v>
+        <v>-1271088000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.86%→0.51%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>40→26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>872872000</v>
+        <v>1613040000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.78%→0.92%</t>
+          <t>0.88%→1.15%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>41→52</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1214,11 +1214,11 @@
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-918008000</v>
+        <v>-939640000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>6.40%→6.08%</t>
+          <t>6.40%→5.96%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
@@ -1234,361 +1234,416 @@
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>3156400000</v>
+        <v>4943120000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>5.72%→6.35%</t>
+          <t>5.72%→7.11%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>80→90</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-868608000</v>
+        <v>-212399200</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2.00%→1.68%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>446472000</v>
+        <v>536536000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.45%</t>
+          <t>0.32%→0.46%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-321152000</v>
+        <v>-305760000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.51%</t>
+          <t>0.16%→0.10%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1331200000</v>
+        <v>939224000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.76%→3.21%</t>
+          <t>0.78%→0.95%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>49→54</t>
+          <t>41→52</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-939848000</v>
+        <v>-470496000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.27%→2.07%</t>
+          <t>1.62%→1.35%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>1038024000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>1.21%→1.46%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>50→59</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>씨메스로보틱스</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-226283200</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>0.29%→0.23%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>64→53</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>444600000</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>1.42%→1.39%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>122→131</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-324480000</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>0.60%→0.50%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>65→57</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>1258400000</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>2.76%→2.91%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>49→54</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-901056000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>2.00%→1.67%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>77→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B25" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>382720000</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>3.25%→2.93%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="C25" s="11" t="n">
+        <v>397800000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>3.25%→2.92%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>166→171</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-947128000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>2.27%→2.00%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>76→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I22" s="15" t="n">
-        <v>-898560000</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>6.61%→6.53%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="I26" s="15" t="n">
+        <v>-887328000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>6.61%→6.18%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>201→195</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="G23" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-1365000000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>3.07%→2.92%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>55→50</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="H23" s="15" t="n">
+      <c r="H28" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I23" s="15" t="n">
-        <v>-334880000</v>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="I28" s="15" t="n">
+        <v>-348920000</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>0.32%→0.22%</t>
         </is>
       </c>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>20→15</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>파마리서치</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>-1219920000</v>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>2.94%→2.64%</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>32→29</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 17억(0.4%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 1종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n">
-        <v>424</v>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>3162573600</v>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.83%</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>0→424</t>
-        </is>
-      </c>
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-123</v>
+        <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1470514200</v>
+        <v>-477984000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>1.16%→0.69%</t>
+          <t>4.34%→4.61%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>345→222</t>
+          <t>184→180</t>
         </is>
       </c>
     </row>
@@ -1600,710 +1655,2035 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-1290120000</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>2.94%→2.67%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>32→29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 61억(1.5%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 7종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>564</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>5468865480</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.37%</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>0→564</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>나이벡  (편출)</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-527</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-4725371850</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>1.18%→0.00%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>527→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>775646250</v>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>3.75%→3.01%</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>999→1,068</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>-155</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>-1889984750</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>1.16%→0.58%</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>345→190</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>796145000</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2.50%→2.65%</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>613→663</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>-1077573000</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>9.46%→9.92%</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>226→220</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>794769600</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>4.84%→5.68%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>659→683</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
           <t>녹십자</t>
         </is>
       </c>
-      <c r="H30" s="15" t="n">
+      <c r="H38" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I30" s="15" t="n">
-        <v>-320045000</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>3.13%→2.98%</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="I38" s="15" t="n">
+        <v>-331683000</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>3.13%→2.96%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>183→178</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
-      <c r="G32" s="19" t="n"/>
-      <c r="H32" s="19" t="n"/>
-      <c r="I32" s="19" t="n"/>
-      <c r="J32" s="19" t="n"/>
-      <c r="K32" s="19" t="n"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="19" t="n"/>
-      <c r="F34" s="19" t="n"/>
-      <c r="G34" s="19" t="n"/>
-      <c r="H34" s="19" t="n"/>
-      <c r="I34" s="19" t="n"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="19" t="n"/>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 3억(0.9%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 7종목  /  매도 10종목</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>코미코  (신규)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1633088000</v>
+        <v>785565000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>0.00%→5.56%</t>
+          <t>9.12%→8.93%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>0→395</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-82</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-55527120</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>7.65%→7.04%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>3,134→3,052</t>
-        </is>
-      </c>
+          <t>797→815</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>94004400</v>
+        <v>752343800</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.39%</t>
+          <t>8.08%→8.03%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>36→191</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>새로닉스</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-43</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-35131000</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>2.80%→2.52%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>950→907</t>
-        </is>
-      </c>
+          <t>540→553</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="17" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>66884560</v>
+        <v>656224500</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.07%→0.29%</t>
+          <t>4.84%→5.11%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>22→101</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
+          <t>90→93</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="n"/>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="17" t="n"/>
+      <c r="J41" s="17" t="n"/>
+      <c r="K41" s="17" t="n"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억   ·   현금 120억(4.3%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 9종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>116</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>788753600</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.30%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>0→116</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-171</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-2262152160</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>2.66%→1.73%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>521→350</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>미래에셋벤처투자</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>1063977200</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>0.54%→0.93%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>126→221</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-130</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-1768821600</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>1.21%→0.61%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>250→120</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>한국피아이엠  (신규)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>1360418400</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.51%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>0→33</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>씨어스  (편출)</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-70</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-1265936000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>0.47%→0.00%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>70→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>1398795200</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2.97%→3.28%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>100→119</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-1212820800</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>4.78%→4.55%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>375→341</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>티에스이  (신규)</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>2584560000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.97%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>0→15</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>메쥬</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-227783040</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.27%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>101→77</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>2616600000</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>1.64%→2.73%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>25→39</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-1100467200</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.41%→0.00%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>24→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>덕산하이메탈</t>
         </is>
       </c>
-      <c r="H41" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-24858080</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>0.60%→0.48%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>227→193</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>60233040</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>1.30%→1.43%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>442→516</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-57228000</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>2.73%→2.38%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>397→367</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>73416000</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>2.54%→2.65%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>144→159</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-46375200</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>6.31%→5.81%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>1,020→993</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱  (신규)</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>58770800</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.20%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>0→11</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-36176000</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>2.99%→2.70%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>321→307</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>43160400</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>3.16%→3.13%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>183→192</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-48571600</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>0.48%→0.29%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>30→19</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>클래시스</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-20307200</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>0.51%→0.41%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>56→48</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>-70376000</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>2.47%→2.10%</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>39→35</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>-40424400</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>1.99%→1.74%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>41→38</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 12억(2.2%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 1종목  /  매도 1종목</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="B52" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>41609280</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>0.58%→0.58%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>218→224</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-1889790400</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>2.00%→1.44%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>70→47</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>73905600</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>0.94%→1.12%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>119→122</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-2272276800</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>5.66%→4.96%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>123→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>76148400</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>1.29%→1.45%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>150→153</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="n"/>
+      <c r="H54" s="17" t="n"/>
+      <c r="I54" s="17" t="n"/>
+      <c r="J54" s="17" t="n"/>
+      <c r="K54" s="17" t="n"/>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 89억(3.8%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 4종목  /  매도 9종목</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>221</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>4703764000</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>1.63%→3.95%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>200→421</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>고영  (편출)</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-2097528000</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>0.90%→0.00%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>194→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>187</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>4558686000</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>1.46%→3.63%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>151→338</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-6937904000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>3.91%→1.10%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>250→66</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>4421598000</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>13.38%→15.13%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>453→520</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-4602750000</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>6.55%→4.29%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>389→264</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>3284400000</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>2.56%→4.03%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>100→156</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-2233392000</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.96%→0.00%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-908293000</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>0.82%→0.40%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>203→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-235824000</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.15%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>199→119</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="n"/>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-685678000</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>0.68%→0.37%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>150→83</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="n"/>
+      <c r="B66" s="17" t="n"/>
+      <c r="C66" s="17" t="n"/>
+      <c r="D66" s="17" t="n"/>
+      <c r="E66" s="17" t="n"/>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>토모큐브</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-429352000</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>0.57%→0.28%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>101→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="n"/>
+      <c r="B67" s="17" t="n"/>
+      <c r="C67" s="17" t="n"/>
+      <c r="D67" s="17" t="n"/>
+      <c r="E67" s="17" t="n"/>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-230724000</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>0.16%→0.06%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>46→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 2억(0.6%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 7종목  /  매도 10종목</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>코미코  (신규)</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>395</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>1633088000</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→5.56%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>0→395</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-55527120</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>7.65%→7.04%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>3,134→3,052</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>94004400</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>0.08%→0.39%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>36→191</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-35131000</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>2.80%→2.52%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>950→907</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>79</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>66884560</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>0.07%→0.29%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>22→101</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-24858080</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>0.60%→0.48%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>227→193</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>60233040</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>1.30%→1.43%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>442→516</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-57228000</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>2.73%→2.38%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>397→367</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>73416000</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>2.54%→2.65%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>144→159</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>-46375200</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>6.31%→5.81%</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>1,020→993</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>58770800</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.20%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>0→11</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>-36176000</v>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>2.99%→2.70%</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>321→307</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>43160400</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>3.16%→3.13%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>183→192</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I78" s="15" t="n">
+        <v>-48571600</v>
+      </c>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>0.48%→0.29%</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>30→19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="n"/>
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="17" t="n"/>
+      <c r="D79" s="17" t="n"/>
+      <c r="E79" s="17" t="n"/>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>-20307200</v>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.41%</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>56→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="n"/>
+      <c r="B80" s="17" t="n"/>
+      <c r="C80" s="17" t="n"/>
+      <c r="D80" s="17" t="n"/>
+      <c r="E80" s="17" t="n"/>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <v>-70376000</v>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>2.47%→2.10%</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>39→35</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="n"/>
+      <c r="B81" s="17" t="n"/>
+      <c r="C81" s="17" t="n"/>
+      <c r="D81" s="17" t="n"/>
+      <c r="E81" s="17" t="n"/>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>-40424400</v>
+      </c>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>1.99%→1.74%</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 5억(0.9%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
           <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n">
-        <v>655</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>1089789000</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.99%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>0→655</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="B86" s="11" t="n">
+        <v>878</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>1899061320</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.32%</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>0→878</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
         <is>
           <t>한스바이오메드</t>
         </is>
       </c>
-      <c r="H53" s="15" t="n">
-        <v>-210</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-472306800</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>2.87%→1.65%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>612→402</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="H86" s="15" t="n">
+        <v>-301</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>-692601000</v>
+      </c>
+      <c r="J86" s="16" t="inlineStr">
+        <is>
+          <t>2.87%→1.25%</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>612→311</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>227</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>953581600</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.67%</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>0→227</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>-576725000</v>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>2.73%→1.02%</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>464→234</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>321774200</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>3.46%→4.34%</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>498→572</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>-507824800</v>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>3.22%→1.78%</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>349→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>287896400</v>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>5.65%→6.35%</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>256→278</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <v>-587640000</v>
+      </c>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>3.71%→2.41%</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>67→47</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B55" s="19" t="n"/>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="19" t="n"/>
-      <c r="G55" s="19" t="n"/>
-      <c r="H55" s="19" t="n"/>
-      <c r="I55" s="19" t="n"/>
-      <c r="J55" s="19" t="n"/>
-      <c r="K55" s="19" t="n"/>
+      <c r="B91" s="19" t="n"/>
+      <c r="C91" s="19" t="n"/>
+      <c r="D91" s="19" t="n"/>
+      <c r="E91" s="19" t="n"/>
+      <c r="F91" s="19" t="n"/>
+      <c r="G91" s="19" t="n"/>
+      <c r="H91" s="19" t="n"/>
+      <c r="I91" s="19" t="n"/>
+      <c r="J91" s="19" t="n"/>
+      <c r="K91" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A34:K34"/>
+  <mergeCells count="21">
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="G70:K70"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="G57:K57"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A91:K91"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="G51:K51"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="G84:K84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260821.xlsx
+++ b/reports/pdf_rolling5_20260821.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 123억(2.6%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 20종목  /  매도 25종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억   ·   현금 82억(1.7%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 20종목  /  매도 25종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>420</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>9522240000</v>
+        <v>9476460000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-283</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2866676800</v>
+        <v>-2852894700</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>149</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>7438080000</v>
+        <v>7402320000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1340310400</v>
+        <v>-1333866600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>461853600</v>
+        <v>459633150</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1343440800</v>
+        <v>-1336981950</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>72</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1950624000</v>
+        <v>1941246000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-3031704000</v>
+        <v>-3017128500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2669472000</v>
+        <v>2656638000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1414816000</v>
+        <v>-1408014000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>478951200</v>
+        <v>476648550</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-36</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-950976000</v>
+        <v>-946404000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>42</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>451651200</v>
+        <v>449479800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-27</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2316600000</v>
+        <v>-2305462500</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>39</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>920712000</v>
+        <v>916285500</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-25</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-3000400000</v>
+        <v>-2985975000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>36</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>449280000</v>
+        <v>447120000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-24</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-968448000</v>
+        <v>-963792000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1013376000</v>
+        <v>1008504000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-464048000</v>
+        <v>-461817000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>885768000</v>
+        <v>881509500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-15</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-901680000</v>
+        <v>-897345000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>411840000</v>
+        <v>409860000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1271088000</v>
+        <v>-1264977000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1613040000</v>
+        <v>1605285000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-939640000</v>
+        <v>-935122500</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>4943120000</v>
+        <v>533956500</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>5.72%→7.11%</t>
+          <t>0.32%→0.46%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>80→94</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1258,7 +1258,7 @@
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-212399200</v>
+        <v>-211378050</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1274,44 +1274,44 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>536536000</v>
+        <v>4919355000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.32%→0.46%</t>
+          <t>5.72%→7.11%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-305760000</v>
+        <v>-468234000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.10%</t>
+          <t>1.62%→1.35%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>939224000</v>
+        <v>934708500</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-470496000</v>
+        <v>-304290000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.62%→1.35%</t>
+          <t>0.16%→0.10%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1038024000</v>
+        <v>1033033500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-226283200</v>
+        <v>-225195300</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>9</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>444600000</v>
+        <v>442462500</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>-8</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-324480000</v>
+        <v>-322920000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1450,23 +1450,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1258400000</v>
+        <v>395887500</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>2.76%→2.91%</t>
+          <t>3.25%→2.92%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>49→54</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1478,7 +1478,7 @@
         <v>-8</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-901056000</v>
+        <v>-896724000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1494,23 +1494,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>397800000</v>
+        <v>1252350000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>3.25%→2.92%</t>
+          <t>2.76%→2.91%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>49→54</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-947128000</v>
+        <v>-942574500</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-887328000</v>
+        <v>-883062000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1571,23 +1571,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1365000000</v>
+        <v>-347242500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.92%</t>
+          <t>0.32%→0.22%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>20→15</t>
         </is>
       </c>
     </row>
@@ -1599,23 +1599,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-348920000</v>
+        <v>-1358437500</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.22%</t>
+          <t>3.07%→2.92%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-477984000</v>
+        <v>-475686000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1290120000</v>
+        <v>-1283917500</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 61억(1.5%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억   ·   현금 40억(1.0%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1774,7 +1774,7 @@
         <v>564</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>5468865480</v>
+        <v>5458527360</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>-527</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-4725371850</v>
+        <v>-4716439200</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>69</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>775646250</v>
+        <v>774180000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>-155</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1889984750</v>
+        <v>-1886412000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>50</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>796145000</v>
+        <v>794640000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>-6</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1077573000</v>
+        <v>-1075536000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>794769600</v>
+        <v>793267200</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>-5</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-331683000</v>
+        <v>-331056000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>785565000</v>
+        <v>784080000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>13</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>752343800</v>
+        <v>750921600</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>656224500</v>
+        <v>654984000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억   ·   현금 120억(4.3%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 9종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억   ·   현금 80억(2.9%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 9종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -2123,7 +2123,7 @@
         <v>116</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>788753600</v>
+        <v>785430200</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>-171</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-2262152160</v>
+        <v>-2252620620</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>95</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1063977200</v>
+        <v>1059494150</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>-130</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1768821600</v>
+        <v>-1761368700</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>33</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1360418400</v>
+        <v>1354686300</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>-70</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1265936000</v>
+        <v>-1260602000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>19</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1398795200</v>
+        <v>1392901400</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>-34</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-1212820800</v>
+        <v>-1207710600</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>2584560000</v>
+        <v>2573670000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2313,23 +2313,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-227783040</v>
+        <v>-1095830400</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.27%</t>
+          <t>0.41%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
         <v>14</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>2616600000</v>
+        <v>2605575000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2357,23 +2357,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1100467200</v>
+        <v>-226823280</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.00%</t>
+          <t>0.34%→0.27%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>41609280</v>
+        <v>41433960</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>-23</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1889790400</v>
+        <v>-1881827800</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2424,23 +2424,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>73905600</v>
+        <v>75827550</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.12%</t>
+          <t>1.29%→1.45%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>119→122</t>
+          <t>150→153</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2452,7 +2452,7 @@
         <v>-18</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-2272276800</v>
+        <v>-2262702600</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2468,23 +2468,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>76148400</v>
+        <v>73594200</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.45%</t>
+          <t>0.94%→1.12%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>150→153</t>
+          <t>119→122</t>
         </is>
       </c>
       <c r="G54" s="17" t="n"/>
@@ -2496,7 +2496,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 89억(3.8%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 4종목  /  매도 9종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억   ·   현금 59억(2.6%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 4종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -2592,7 +2592,7 @@
         <v>221</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>4703764000</v>
+        <v>4662260200</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>-194</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-2097528000</v>
+        <v>-2079020400</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>187</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>4558686000</v>
+        <v>4518462300</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>-184</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-6937904000</v>
+        <v>-6876687200</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>67</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>4421598000</v>
+        <v>4382583900</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>-125</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-4602750000</v>
+        <v>-4562137500</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>56</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>3284400000</v>
+        <v>3255420000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>-102</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-2233392000</v>
+        <v>-2213685600</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>-101</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-908293000</v>
+        <v>-900278650</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>-80</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-235824000</v>
+        <v>-233743200</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>-67</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-685678000</v>
+        <v>-679627900</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>-41</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-429352000</v>
+        <v>-425563600</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>-29</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-230724000</v>
+        <v>-228688200</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 2억(0.6%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 7종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억   ·   현금 2억(0.6%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 7종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B69" s="4" t="n"/>
@@ -2997,11 +2997,11 @@
         <v>395</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>1633088000</v>
+        <v>1590112000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>0.00%→5.56%</t>
+          <t>0.00%→5.45%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -3018,11 +3018,11 @@
         <v>-82</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-55527120</v>
+        <v>-54369280</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>7.65%→7.04%</t>
+          <t>7.53%→6.94%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -3041,11 +3041,11 @@
         <v>155</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>94004400</v>
+        <v>94054000</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.39%</t>
+          <t>0.08%→0.40%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -3062,11 +3062,11 @@
         <v>-43</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-35131000</v>
+        <v>-35511120</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.52%</t>
+          <t>2.84%→2.57%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -3085,7 +3085,7 @@
         <v>79</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>66884560</v>
+        <v>65416740</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
@@ -3106,11 +3106,11 @@
         <v>-34</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-24858080</v>
+        <v>-24505840</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.48%</t>
+          <t>0.59%→0.48%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -3129,11 +3129,11 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>60233040</v>
+        <v>59359840</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>1.30%→1.43%</t>
+          <t>1.29%→1.42%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -3150,11 +3150,11 @@
         <v>-30</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-57228000</v>
+        <v>-57165000</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2.73%→2.38%</t>
+          <t>2.74%→2.40%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3173,11 +3173,11 @@
         <v>15</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>73416000</v>
+        <v>74481000</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>2.54%→2.65%</t>
+          <t>2.59%→2.71%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -3194,7 +3194,7 @@
         <v>-27</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-46375200</v>
+        <v>-46053900</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>11</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>58770800</v>
+        <v>58363800</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
@@ -3238,11 +3238,11 @@
         <v>-14</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-36176000</v>
+        <v>-36933400</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2.99%→2.70%</t>
+          <t>3.07%→2.78%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3261,11 +3261,11 @@
         <v>9</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>43160400</v>
+        <v>41758200</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>3.16%→3.13%</t>
+          <t>3.08%→3.05%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3282,11 +3282,11 @@
         <v>-11</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-48571600</v>
+        <v>-47049200</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.29%</t>
+          <t>0.47%→0.28%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -3310,11 +3310,11 @@
         <v>-8</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>-20307200</v>
+        <v>-19891200</v>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.41%</t>
+          <t>0.50%→0.41%</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -3338,11 +3338,11 @@
         <v>-4</v>
       </c>
       <c r="I80" s="15" t="n">
-        <v>-70376000</v>
+        <v>-67932000</v>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>2.47%→2.10%</t>
+          <t>2.40%→2.04%</t>
         </is>
       </c>
       <c r="K80" s="13" t="inlineStr">
@@ -3366,11 +3366,11 @@
         <v>-3</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>-40424400</v>
+        <v>-37451400</v>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>1.99%→1.74%</t>
+          <t>1.86%→1.63%</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 5억(0.9%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억   ·   현금 5억(0.9%)      오늘 2026-08-21  vs  5일전 2026-08-13      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B83" s="4" t="n"/>
@@ -3478,7 +3478,7 @@
         <v>878</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>1899061320</v>
+        <v>1915155060</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>-301</v>
       </c>
       <c r="I86" s="15" t="n">
-        <v>-692601000</v>
+        <v>-698470500</v>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>227</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>953581600</v>
+        <v>961662800</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>-230</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>-576725000</v>
+        <v>-581612500</v>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>74</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>321774200</v>
+        <v>324501100</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>-116</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-507824800</v>
+        <v>-512128400</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>22</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>287896400</v>
+        <v>290336200</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>-20</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-587640000</v>
+        <v>-592620000</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260821.xlsx
+++ b/reports/pdf_rolling5_20260821.xlsx
@@ -2313,23 +2313,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1095830400</v>
+        <v>-226823280</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.00%</t>
+          <t>0.34%→0.27%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2357,23 +2357,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-226823280</v>
+        <v>-1095830400</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.27%</t>
+          <t>0.41%→0.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260821.xlsx
+++ b/reports/pdf_rolling5_20260821.xlsx
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-468234000</v>
+        <v>-304290000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.62%→1.35%</t>
+          <t>0.16%→0.10%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-304290000</v>
+        <v>-468234000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.10%</t>
+          <t>1.62%→1.35%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1033033500</v>
+        <v>442462500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.21%→1.46%</t>
+          <t>1.42%→1.39%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1406,111 +1406,111 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>442462500</v>
+        <v>1033033500</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.39%</t>
+          <t>1.21%→1.46%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-322920000</v>
+        <v>-896724000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.50%</t>
+          <t>2.00%→1.67%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>395887500</v>
+        <v>1252350000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>3.25%→2.92%</t>
+          <t>2.76%→2.91%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>49→54</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-896724000</v>
+        <v>-322920000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>2.00%→1.67%</t>
+          <t>0.60%→0.50%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>65→57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1252350000</v>
+        <v>395887500</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2.76%→2.91%</t>
+          <t>3.25%→2.92%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>49→54</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -2313,23 +2313,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-226823280</v>
+        <v>-1095830400</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.27%</t>
+          <t>0.41%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2357,23 +2357,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1095830400</v>
+        <v>-226823280</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.00%</t>
+          <t>0.34%→0.27%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2424,23 +2424,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>75827550</v>
+        <v>73594200</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.45%</t>
+          <t>0.94%→1.12%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>150→153</t>
+          <t>119→122</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2468,23 +2468,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>73594200</v>
+        <v>75827550</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.12%</t>
+          <t>1.29%→1.45%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>119→122</t>
+          <t>150→153</t>
         </is>
       </c>
       <c r="G54" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260821.xlsx
+++ b/reports/pdf_rolling5_20260821.xlsx
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>533956500</v>
+        <v>4919355000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.32%→0.46%</t>
+          <t>5.72%→7.11%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>80→94</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1274,23 +1274,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>4919355000</v>
+        <v>533956500</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>5.72%→7.11%</t>
+          <t>0.32%→0.46%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>80→94</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1362,23 +1362,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>442462500</v>
+        <v>1033033500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.39%</t>
+          <t>1.21%→1.46%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>50→59</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1406,111 +1406,111 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1033033500</v>
+        <v>442462500</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.21%→1.46%</t>
+          <t>1.42%→1.39%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-896724000</v>
+        <v>-322920000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2.00%→1.67%</t>
+          <t>0.60%→0.50%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>65→57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1252350000</v>
+        <v>395887500</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>2.76%→2.91%</t>
+          <t>3.25%→2.92%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>49→54</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-322920000</v>
+        <v>-896724000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.50%</t>
+          <t>2.00%→1.67%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>395887500</v>
+        <v>1252350000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>3.25%→2.92%</t>
+          <t>2.76%→2.91%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>49→54</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -1571,23 +1571,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-347242500</v>
+        <v>-1358437500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.22%</t>
+          <t>3.07%→2.92%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1599,23 +1599,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1358437500</v>
+        <v>-347242500</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.92%</t>
+          <t>0.32%→0.22%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>20→15</t>
         </is>
       </c>
     </row>
@@ -2313,23 +2313,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1095830400</v>
+        <v>-226823280</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.00%</t>
+          <t>0.34%→0.27%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2357,23 +2357,23 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-226823280</v>
+        <v>-1095830400</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.27%</t>
+          <t>0.41%→0.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2424,23 +2424,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>73594200</v>
+        <v>75827550</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.12%</t>
+          <t>1.29%→1.45%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>119→122</t>
+          <t>150→153</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2468,23 +2468,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>75827550</v>
+        <v>73594200</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.45%</t>
+          <t>0.94%→1.12%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>150→153</t>
+          <t>119→122</t>
         </is>
       </c>
       <c r="G54" s="17" t="n"/>
